--- a/files/inclass/korean/IC_L8_skhynix_fcff.xlsx
+++ b/files/inclass/korean/IC_L8_skhynix_fcff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hong1p\Dropbox\1_0_teaching\0_2026_Summer\0_Kaist MBA\1_weekly notes\0_Valuation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D720615-4C23-405F-94D9-95951CC1930E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFA1E77-4CA2-45CB-8697-D622F0E2CC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2145" windowWidth="29040" windowHeight="15195" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="2145" windowWidth="29040" windowHeight="15195" tabRatio="500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Consensus" sheetId="5" r:id="rId5"/>
     <sheet name="1) DCF Val_FCFF" sheetId="7" r:id="rId6"/>
     <sheet name="2) VAL with Earnings" sheetId="8" r:id="rId7"/>
-    <sheet name="3) VAL Goldens Growth Model" sheetId="9" r:id="rId8"/>
+    <sheet name="3) VAL Gordon Growth Model" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -8299,14 +8299,14 @@
     <xf numFmtId="3" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11741,34 +11741,34 @@
       <c r="A6" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D6" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="49" t="s">
+      <c r="F6" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="49" t="s">
+      <c r="G6" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="H6" s="49" t="s">
+      <c r="H6" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="I6" s="49" t="s">
+      <c r="I6" s="48" t="s">
         <v>135</v>
       </c>
-      <c r="J6" s="49" t="s">
+      <c r="J6" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="K6" s="49" t="s">
+      <c r="K6" s="48" t="s">
         <v>65</v>
       </c>
     </row>
@@ -12392,28 +12392,28 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1">
-      <c r="A14" s="48" t="s">
+      <c r="A14" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="B14" s="48"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="48"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
     </row>
     <row r="16" spans="1:4" ht="30" customHeight="1">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12686,7 +12686,7 @@
       <c r="A27" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="48" t="s">
         <v>203</v>
       </c>
       <c r="D27" s="14" t="s">
@@ -12704,7 +12704,7 @@
       <c r="H27" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="I27" s="48" t="s">
         <v>209</v>
       </c>
     </row>
@@ -12728,7 +12728,7 @@
       <c r="H28" s="23">
         <v>0.05</v>
       </c>
-      <c r="L28" s="50" t="s">
+      <c r="L28" s="49" t="s">
         <v>261</v>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>265</v>
       </c>
     </row>
@@ -13679,7 +13679,7 @@
       <c r="A27" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="48" t="s">
         <v>203</v>
       </c>
       <c r="D27" s="14" t="s">
@@ -13697,7 +13697,7 @@
       <c r="H27" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="I27" s="48" t="s">
         <v>209</v>
       </c>
     </row>
@@ -13780,27 +13780,27 @@
         <v>210</v>
       </c>
       <c r="C31" s="17">
-        <f>C29*C30</f>
+        <f t="shared" ref="C31:H31" si="0">C29*C30</f>
         <v>47206</v>
       </c>
       <c r="D31" s="17">
-        <f>D29*D30</f>
+        <f t="shared" si="0"/>
         <v>199345.644</v>
       </c>
       <c r="E31" s="17">
-        <f>E29*E30</f>
+        <f t="shared" si="0"/>
         <v>197407.56134999997</v>
       </c>
       <c r="F31" s="17">
-        <f>F29*F30</f>
+        <f t="shared" si="0"/>
         <v>83579.814281249986</v>
       </c>
       <c r="G31" s="17">
-        <f>G29*G30</f>
+        <f t="shared" si="0"/>
         <v>87758.804995312501</v>
       </c>
       <c r="H31" s="17">
-        <f>H29*H30</f>
+        <f t="shared" si="0"/>
         <v>89513.981095218769</v>
       </c>
     </row>
@@ -13827,27 +13827,27 @@
         <v>263</v>
       </c>
       <c r="C40" s="38">
-        <f>C31</f>
+        <f t="shared" ref="C40:H40" si="1">C31</f>
         <v>47206</v>
       </c>
       <c r="D40" s="38">
-        <f>D31</f>
+        <f t="shared" si="1"/>
         <v>199345.644</v>
       </c>
       <c r="E40" s="38">
-        <f>E31</f>
+        <f t="shared" si="1"/>
         <v>197407.56134999997</v>
       </c>
       <c r="F40" s="38">
-        <f>F31</f>
+        <f t="shared" si="1"/>
         <v>83579.814281249986</v>
       </c>
       <c r="G40" s="38">
-        <f>G31</f>
+        <f t="shared" si="1"/>
         <v>87758.804995312501</v>
       </c>
       <c r="H40" s="38">
-        <f>H31</f>
+        <f t="shared" si="1"/>
         <v>89513.981095218769</v>
       </c>
     </row>
@@ -14069,7 +14069,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="50" t="s">
         <v>266</v>
       </c>
     </row>
@@ -14235,7 +14235,7 @@
       <c r="A27" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="48" t="s">
         <v>203</v>
       </c>
       <c r="D27" s="14" t="s">
@@ -14253,7 +14253,7 @@
       <c r="H27" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="I27" s="49" t="s">
+      <c r="I27" s="48" t="s">
         <v>209</v>
       </c>
     </row>
@@ -14335,27 +14335,27 @@
         <v>263</v>
       </c>
       <c r="C40" s="38">
-        <f>C31</f>
+        <f t="shared" ref="C40:H40" si="0">C31</f>
         <v>0</v>
       </c>
       <c r="D40" s="38">
-        <f>D31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E40" s="38">
-        <f>E31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F40" s="38">
-        <f>F31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G40" s="38">
-        <f>G31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H40" s="38">
-        <f>H31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/files/inclass/korean/IC_L8_skhynix_fcff.xlsx
+++ b/files/inclass/korean/IC_L8_skhynix_fcff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hong1p\Dropbox\1_0_teaching\0_2026_Summer\0_Kaist MBA\1_weekly notes\0_Valuation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFA1E77-4CA2-45CB-8697-D622F0E2CC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB187835-A323-4B0C-AE10-4003468419FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2145" windowWidth="29040" windowHeight="15195" tabRatio="500" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="390" windowWidth="19420" windowHeight="10990" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -8133,7 +8133,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8164,6 +8164,18 @@
         <bgColor rgb="FFEAF0FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFEAF0FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -8192,7 +8204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8306,6 +8318,21 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12428,6 +12455,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.59999389629810485"/>
+  </sheetPr>
   <dimension ref="A1:L72"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
@@ -13031,31 +13061,31 @@
         <v>-1880.5458213281293</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
-      <c r="A40" s="32" t="s">
+    <row r="40" spans="1:12" s="53" customFormat="1">
+      <c r="A40" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="C40" s="38">
+      <c r="C40" s="54">
         <f>Raw_SKhynix!K42</f>
         <v>25854</v>
       </c>
-      <c r="D40" s="39">
+      <c r="D40" s="55">
         <f>D33+D35+D37+D39</f>
         <v>81463.588320000024</v>
       </c>
-      <c r="E40" s="39">
+      <c r="E40" s="55">
         <f>E33+E35+E37+E39</f>
         <v>99988.452602999983</v>
       </c>
-      <c r="F40" s="39">
+      <c r="F40" s="55">
         <f>F33+F35+F37+F39</f>
         <v>46088.297589374983</v>
       </c>
-      <c r="G40" s="39">
+      <c r="G40" s="55">
         <f>G33+G35+G37+G39</f>
         <v>39079.533163218752</v>
       </c>
-      <c r="H40" s="39">
+      <c r="H40" s="55">
         <f>H33+H35+H37+H39</f>
         <v>44245.482084208139</v>
       </c>
@@ -13279,10 +13309,10 @@
       </c>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="32" t="s">
+      <c r="A59" s="52" t="s">
         <v>240</v>
       </c>
-      <c r="B59" s="39">
+      <c r="B59" s="55">
         <f>SUM(B54:B58)</f>
         <v>538352.6111504453</v>
       </c>
@@ -13297,19 +13327,19 @@
       </c>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="32" t="s">
+      <c r="A61" s="52" t="s">
         <v>241</v>
       </c>
-      <c r="B61" s="45">
+      <c r="B61" s="56">
         <f>B59*B7/B6</f>
         <v>736974.64872954506</v>
       </c>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="57" t="s">
         <v>242</v>
       </c>
-      <c r="B62" s="46">
+      <c r="B62" s="58">
         <f>B5</f>
         <v>1577000</v>
       </c>
